--- a/output/reports/cv_experiment_Stacking_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_Stacking_qcut_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>26.63461375236511</v>
+        <v>2.186573266983032</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999999989381</v>
+        <v>0.9919591707630674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999999999980579</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002479899541464002</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001843707740354632</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>41.420814037323</v>
+        <v>2.433193683624268</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999999999944957</v>
+        <v>0.9922542316820335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999999999980579</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002479899541464002</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001843707740354632</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>81.46107649803162</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9999999999930822</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9999999999980579</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.0002479899541464002</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0001843707740354632</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>115.8153793811798</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9999999999848707</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9999999999993684</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0001414200199542172</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0001126384883517061</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>26.63461375236511</v>
+        <v>2.186573266983032</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999999989381</v>
+        <v>0.9919591707630674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999999999980579</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002479899541464002</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001843707740354632</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>41.420814037323</v>
+        <v>2.433193683624268</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999999999944957</v>
+        <v>0.9922542316820335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999999999980579</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002479899541464002</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001843707740354632</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>81.46107649803162</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9999999999930822</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9999999999980579</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.0002479899541464002</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0001843707740354632</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>115.8153793811798</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9999999999848707</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9999999999993684</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0001414200199542172</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0001126384883517061</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
